--- a/testdata/LoginData.xlsx
+++ b/testdata/LoginData.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\IdeaProjects\AutomateEcomm\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCD509F-1A5A-4996-AA1C-5927DC33FFE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC2A22D-DFB7-4D0F-A37D-6DA04D0B13AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{349C4EB3-7C07-406A-AB59-EA06CA10F150}"/>
+    <workbookView xWindow="1100" yWindow="1100" windowWidth="14400" windowHeight="7270" xr2:uid="{349C4EB3-7C07-406A-AB59-EA06CA10F150}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -59,10 +60,19 @@
     <t>res</t>
   </si>
   <si>
+    <t>Invalid</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Learn Selenium</t>
+  </si>
+  <si>
+    <t>Awesome techies</t>
+  </si>
+  <si>
     <t>Valid</t>
-  </si>
-  <si>
-    <t>Invalid</t>
   </si>
 </sst>
 </file>
@@ -459,6 +469,7 @@
   <cols>
     <col min="1" max="1" width="28.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -480,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -491,7 +502,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -501,4 +512,45 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48AD3186-60F6-4449-AE9A-8CDC57353D2E}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="2" width="26.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{4E3FE668-D658-4006-960C-6BFB7552F83F}"/>
+    <hyperlink ref="A3" r:id="rId2" display="Pass@123" xr:uid="{52980AAF-F14D-4A6C-AA1B-431812BDF8BA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>